--- a/光伏配储项目/电价数据/2026/皇岗站.xlsx
+++ b/光伏配储项目/电价数据/2026/皇岗站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.7710399999999999</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.3846</v>
+      </c>
+      <c r="C117" t="n">
+        <v>1.03266</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.8623500000000001</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.59275</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.73722</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.77639</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.44268</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.46035</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.43242</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42709</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.42536</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.41336</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.40086</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.40037</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.38815</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.4052</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.42868</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41717</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35584</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39509</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.38821</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.42097</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39547</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.42486</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.41788</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.42805</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41557</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44794</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.50304</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.40132</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30827</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.31169</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.32795</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.35128</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.37439</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.32276</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.3519</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.13091</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.14405</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.3382</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.14888</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.08473</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.12305</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.48513</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.2112</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.31439</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.28826</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.05221</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.9775199999999999</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>1.54715</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.1491</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.22166</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.23074</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.236</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.21995</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.8611</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.27993</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.47402</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.15687</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.34836</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.36217</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.29046</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.29569</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.48379</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.6482899999999999</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.73864</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.86198</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.7305700000000001</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.53854</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.39439</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.43116</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.43629</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.6577999999999999</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>1.22584</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.8334</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.56297</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.41387</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.64278</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.80214</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>1.04521</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>1.1018</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.68848</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>1.281</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.8699600000000001</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.79613</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.75666</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.5174500000000001</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.47918</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.4687</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41557</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42519</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.70789</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.76746</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.86983</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.914</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.49354</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.51375</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50184</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.50208</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.48439</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.39899</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.46657</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.37779</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.3777799999999999</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.37582</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33616</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.36515</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35059</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.35054</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.36204</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.36606</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.34967</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.3724</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.40511</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.8550800000000001</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.7004</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.79583</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.45335</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.43387</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.377</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34739</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.38706</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.42661</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.50876</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.35475</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.33939</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.35661</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.33205</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.33223</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.38135</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.30246</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.33281</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.34377</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.37841</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.51401</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.78576</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.9999600000000001</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.3371499999999999</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.52901</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.89603</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.85162</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.50422</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.7356900000000001</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>1.55335</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>1.09692</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>1.03181</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.30015</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.35165</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.37736</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.47398</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.5495399999999999</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.50312</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.52488</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.90939</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.62193</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.9095</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>1.21109</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.46612</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.17711</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>1.06436</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.5127</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.41507</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.57075</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.34973</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.39999</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.95672</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>1.29227</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.9009299999999999</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>1.35986</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>1.41395</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>1.28683</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>1.07729</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.44985</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.79014</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.8103899999999999</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.44866</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.42785</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.4433</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33349</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37546</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35457</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33457</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.50705</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.48614</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.48648</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.37782</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.44721</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.41376</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.3683</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.38895</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38243</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36292</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.42718</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.44254</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33562</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.36983</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39515</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.3666</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.3675</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35545</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.3609</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35153</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.3622</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35659</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.38286</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39465</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47147</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.4436</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.43739</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34722</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39398</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35261</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36725</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34732</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.47684</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.6162799999999999</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.84766</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.77787</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.7187899999999999</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.24222</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.39624</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.37693</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.33164</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.37687</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.41097</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.42468</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.56599</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.5103</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.82978</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.41238</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.60348</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.7301799999999999</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.81817</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.52884</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.54664</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.7979400000000001</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>1.18854</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.6800900000000001</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.60278</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.49427</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.46037</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.4238</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.39428</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.7571</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.5195700000000001</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.50543</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.5709</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.59709</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.54692</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.5670299999999999</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.2614</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.6155499999999999</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>1.06184</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.49534</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.5287999999999999</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.5717100000000001</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.9063600000000001</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.95087</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>1.36765</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.7559199999999999</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.7694099999999999</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.62163</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.83412</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.60915</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.8571299999999999</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.5625800000000001</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>1.19869</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.82574</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.5616100000000001</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.48572</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.61922</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.50776</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.45639</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.39723</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36204</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34844</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34191</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.5213</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.49319</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.44428</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.38906</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.38904</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.34792</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.36686</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.35876</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.38724</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.38539</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.36125</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.44819</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.3597</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.34837</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.36281</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.35727</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.35836</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.33732</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.33486</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.33148</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.33396</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.33139</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33882</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35087</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.38492</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.38825</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.34845</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.37459</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.34388</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.3931</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.41574</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.5047</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.35644</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.6864600000000001</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.34045</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.57797</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.78923</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>1.06213</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.71704</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.8009500000000001</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>1.23086</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.62015</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>1.30926</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>1.15041</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>1.06134</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.85024</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>1.32834</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.86448</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.35076</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.35716</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.44757</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.6023999999999999</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.40801</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.33523</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.32075</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.34775</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.48114</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.40618</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.39831</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.8130599999999999</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.8206100000000001</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.7287899999999999</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>1.27077</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>1.26511</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.42533</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.49343</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.45023</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.46096</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.39939</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.47352</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.5212</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.9407799999999999</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.83116</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>1.27456</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.89025</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.7987799999999999</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.50068</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.73049</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.68667</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.59749</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.41533</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.50617</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.50649</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.34624</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.34143</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.31902</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32302</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.32039</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.31397</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31806</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.31969</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.31669</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.69492</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.80459</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.38239</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.36145</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.36141</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.3291</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.32804</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.33215</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.32074</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31902</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.31609</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31881</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.31851</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31514</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.31641</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.31293</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.31432</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.31945</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.31605</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.31076</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.31012</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31339</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31468</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.3326</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.32113</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.32244</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.32052</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.33269</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.4362799999999999</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.3127200000000001</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.28649</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.33075</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.32579</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.30964</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.3187</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.3038</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.30498</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.2047</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.42155</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.38675</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.22639</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.15473</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.28945</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0.29386</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.36215</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.27321</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.19453</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.42008</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0.39624</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.06516</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.38249</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.37975</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.22629</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.39339</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.21278</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.06566</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>0.09772</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>0.0147</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>1.19536</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.27038</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.2976</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.29996</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.30811</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.32269</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.3154</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31546</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33572</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33585</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.33317</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.37523</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.38109</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.37555</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.37033</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.35697</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.38712</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39073</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.39923</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.45984</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.37011</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.38915</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.39052</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.48298</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35185</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35646</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34428</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35366</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.34276</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.3656</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.57487</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.37585</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.39624</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.38048</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.37434</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.35137</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.34162</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.35012</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.29838</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.29899</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.27994</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.32969</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.25358</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.33991</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.33645</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.32774</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.27858</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.31014</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.306</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.29083</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.29023</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.28633</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.32803</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.31701</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.33072</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.34473</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.30812</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.30413</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10283</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04361</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04697999999999999</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.0441</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04476</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04398</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.35775</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.01535</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.21638</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.05433</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>0.29043</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.20618</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0.08137999999999999</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04392</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.0456</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04369</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04335</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04549</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04339</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>0.27398</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.04529</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04525</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04538</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04358</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04423</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.07053</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.06877</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04471</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04984</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.0474</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04790999999999999</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19975</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14272</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28994</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30454</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29282</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29329</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29225</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29678</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29074</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29497</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26875</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30855</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31839</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34705</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.34685</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.33972</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.35956</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.35926</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33064</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.32343</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.31154</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31029</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.39347</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.34425</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32031</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30704</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31463</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28114</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29442</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28802</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27116</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27089</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17236</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.1586</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17092</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.1477</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15943</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15858</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23612</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22651</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26883</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28566</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.28069</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28043</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27071</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28091</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30938</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31625</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29731</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.38755</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.37934</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.42736</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.455</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33182</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41845</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41528</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.38592</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40242</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29929</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15654</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.2943</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31094</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31343</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31269</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34628</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30067</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33083</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38546</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5076700000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6220399999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.7851900000000001</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49797</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.7810199999999999</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92039</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49456</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9142100000000001</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.8628899999999999</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.29622</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35366</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.88751</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.6316000000000001</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18709</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.87864</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>1.23478</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33086</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.03292</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.53079</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.79099</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.7785700000000001</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.77298</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.77755</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8767699999999999</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87387</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49315</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.39868</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.3999</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44995</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.207</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87883</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55102</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62186</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53832</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49769</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45582</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42425</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43714</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.44952</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38817</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45268</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.41962</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.34607</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.3982</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36231</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38324</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.40809</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.42508</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.33894</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.38634</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.34496</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.32902</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.33937</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.38142</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34745</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.44901</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.34552</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.39122</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.38095</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.5534</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.40699</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.58202</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.7025399999999999</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.8757</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.46584</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.38689</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.5465399999999999</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.43056</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.8051900000000001</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.55875</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.85109</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.87498</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.3409</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.41398</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.6155</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.32959</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.30233</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.29261</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.62064</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.59116</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>1.06393</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31056</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.35183</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.32976</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32078</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.40648</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.33371</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31698</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.31954</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31907</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.31952</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.33446</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.31767</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.30788</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.31866</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.30115</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29586</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.31116</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.30912</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.31049</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.28257</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.29866</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.30233</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.31136</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.30848</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.31415</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.34714</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.32888</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.33307</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.33096</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.32326</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.32696</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.32527</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.38423</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.3863</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.41804</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.38816</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.37091</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.35469</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.34689</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32835</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.91308</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.34784</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.4401600000000001</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.40338</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.39083</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.43222</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.36418</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.38654</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.35058</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.35336</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.33925</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.3387</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.33342</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.32341</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.34652</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.33496</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.31653</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.3736</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.45505</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.34432</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.36586</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.33241</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.33809</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.34135</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.35309</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.34392</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.3477</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.30568</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.30849</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.32393</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.32808</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.33019</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.33954</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.3122200000000001</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.31065</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.28744</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.31275</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.31508</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.30136</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.19368</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.3043</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30794</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.34276</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.33466</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.36312</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.31121</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.27297</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.19738</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.30435</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.29876</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.31961</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.28081</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.30846</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.30892</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.34685</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.3549</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.30719</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.29983</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.30825</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.31111</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.30924</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.29415</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.29426</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.29851</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.30552</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.30526</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.28806</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.33514</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.25313</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.33558</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.31079</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.32476</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.3268</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.27377</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.33371</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.32712</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.30014</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.33576</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.3268</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.36607</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.3384</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.40654</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.31823</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.33101</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.41933</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.34302</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.43793</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.32494</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.39661</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.3501</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.37619</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.3737799999999999</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.5222599999999999</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.31571</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.8610099999999999</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.43767</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.13328</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.6831499999999999</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.7733099999999999</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.6349900000000001</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.49199</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.39184</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.43768</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.48751</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.42819</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.41213</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.40293</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.40272</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.4007</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.45579</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.40301</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.42336</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.3849</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.42413</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.38289</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.39473</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.41182</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.38661</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.41459</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.40014</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.40305</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.40611</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.37373</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.38871</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.38879</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.37465</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.48481</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.35586</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.30071</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.2859</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.34046</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.35397</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.30467</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.3327</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.30376</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.30581</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.29826</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.5192899999999999</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.35548</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.21294</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.24793</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.30006</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.1544</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.27316</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.27516</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>-0.01157</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.33414</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30111</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.25934</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.25222</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.28138</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.29175</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.30558</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.28856</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.30326</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.31008</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.31775</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.31662</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.31017</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.3261</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.32792</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.38454</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.38117</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.34257</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.35108</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.3315</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.31896</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.35828</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.33321</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.34143</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.35265</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.35283</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.33982</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.5374800000000001</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.42749</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.77615</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.42865</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.46145</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.36194</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.43666</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.36666</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.35395</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.32312</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.32115</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.31868</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.30438</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.38382</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.31644</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.31861</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.29393</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.3276</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.29028</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.29448</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.28861</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.29041</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.2805</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.28866</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.30682</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.30516</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.30971</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.3058</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.27543</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.27556</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.29867</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.31346</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.30129</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.231</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.28336</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.34227</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.2353</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.31102</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.3470299999999999</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.32522</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.32698</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.32854</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.32288</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.31538</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.28999</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.31069</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.23275</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.32055</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.26841</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.26009</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.3119</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.36029</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.23019</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.25126</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.34075</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.32864</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.37756</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.2453</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.2812</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.32041</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.3425</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.28829</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.31054</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.30751</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.30573</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.29137</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.25587</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.31146</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.35471</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.26358</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.28171</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.32808</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.31056</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.46169</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.352</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.40672</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31833</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.36453</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.35527</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.42953</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.33259</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.36097</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.33592</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.37602</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.34375</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.3623</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.41136</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.37356</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.36766</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.37476</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.37274</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.41578</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.4034700000000001</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.40412</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.40847</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.43682</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.39317</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.38133</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.38915</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.38307</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.34077</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.34176</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.32335</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.33215</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.32684</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.48308</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.38145</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.42981</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.39534</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.38889</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.35272</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.36145</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.36037</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.37135</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.37229</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.36282</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.36325</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.34694</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.37119</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.35443</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.36028</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.33696</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.33463</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.34157</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.33272</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.32894</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.33311</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.32893</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.33804</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.41396</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.35213</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.36103</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.34552</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.33067</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.32834</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.33086</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.31985</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.33205</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.3389</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.35371</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.29404</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.31623</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.32811</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.32215</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.29932</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.31271</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.29806</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.9622200000000001</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.75586</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.35082</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.38653</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.25416</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.27901</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30088</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.30132</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31807</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.3177</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.31742</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.35852</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.31354</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.32251</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.23939</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.31214</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.3026</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.31958</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.48572</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.49129</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.41689</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.53986</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.50512</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.40438</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.33307</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.73983</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.8139500000000001</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.3735</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.39711</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.34087</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.39577</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.76858</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.95311</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.6872699999999999</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.99052</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>1.1975</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.37756</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.37071</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.41395</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.41233</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.40745</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.6547999999999999</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.34006</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.34275</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.45401</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.35731</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.4066</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.35765</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.36324</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.36708</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.33884</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.34673</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.33496</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.35167</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.45348</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.36321</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.46633</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.36338</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.34064</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.34979</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.34341</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.33559</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.32967</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.33431</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.33375</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.3371499999999999</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.33929</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.33588</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.33146</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.3306</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.33549</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.33095</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.32709</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.33227</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.328</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.32922</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.33213</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.33662</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.3581</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.37265</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.3659</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.35967</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.41806</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.33068</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.75961</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.87619</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.85861</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>1.45661</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.7722100000000001</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>1.46346</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>1.14223</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.8542000000000001</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.83787</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>1.10987</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.80859</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>1.30191</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>1.17219</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>1.20741</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.75895</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>1.20099</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.41256</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>1.39338</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.6002999999999999</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>1.40733</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>1.27285</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>1.44504</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>1.72903</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>1.57629</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>1.45164</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>1.57774</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>1.23552</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>1.51961</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.92287</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.69716</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>1.25038</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.70385</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.6717000000000001</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.7594</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.68886</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.6828</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>1.20171</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.8091</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>1.5433</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.7883</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.7702</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>1.04545</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.7180700000000001</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.63914</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.59689</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.5092</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.36702</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.50225</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.239</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.36779</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.35119</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.32796</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.33863</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.33325</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.31079</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.33679</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.63946</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.30501</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32002</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.51578</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.39286</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.4121</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.33506</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.32037</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.33209</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.34844</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.30877</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.38474</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.35962</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.32701</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32195</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.32143</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.31587</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.31339</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.37118</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.32496</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.29504</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.28279</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.29889</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.31227</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.31545</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.31006</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.29477</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.29965</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.31056</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.3127799999999999</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.3038</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.28998</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.31527</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.30687</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.32829</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.34812</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.37161</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.37002</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.3267</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>1.00511</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.36081</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.341</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.46494</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.34155</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.32973</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.31374</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.33156</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.33137</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.30859</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.27568</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.32316</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.33446</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.31133</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.31754</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.31984</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.3265</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.33221</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.32756</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.31548</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.30446</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.30813</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.30983</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.79265</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.33528</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>1.11088</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>1.39075</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>1.03477</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.50239</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.32924</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.35374</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.36516</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.3407</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.33794</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.33725</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.79138</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.37004</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.78737</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.3376</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.34941</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.3566</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.34851</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.33931</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.3497</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.34645</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.35247</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.35705</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.36117</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.36376</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.35748</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.3469100000000001</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.35397</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.3572</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.32037</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.3017</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.34239</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.3201</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34199</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.3276</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.34278</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.34177</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.34279</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.34375</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.34322</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.34242</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.33196</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34178</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.33863</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.26404</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.33942</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.33294</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.33319</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.32091</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.33196</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.33242</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.32586</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.34736</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.31676</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.32423</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.33208</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.33271</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.32359</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.32268</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.33742</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.32273</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.33426</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.33414</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.32868</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.32493</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.31452</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.33214</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.32834</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.31706</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.32339</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.29897</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.31751</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.32104</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.32375</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.32275</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.31403</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.32292</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.31442</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.31547</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.32295</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32029</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32859</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31753</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.36968</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.3368</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.31916</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.71951</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>1.25298</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.41419</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.53379</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.41858</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.38377</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.40984</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.4854</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.3405</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.36151</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.33289</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34911</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.34919</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.57259</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.37948</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.3461</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.352</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.40984</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.34363</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.38014</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.42948</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.34777</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.35114</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.39829</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.3410899999999999</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.36836</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.47854</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.41367</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.36933</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.40174</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.59128</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.37166</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.36818</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.6497200000000001</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.4239</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.6134299999999999</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.58453</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.85185</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.34275</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.69114</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.35163</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.33205</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.33237</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32207</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.40346</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.36859</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.35858</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.35435</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.3515</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.35116</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.35433</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.35042</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.34873</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.35128</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.34514</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.35229</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.34799</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.34843</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.34438</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.34696</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.35179</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35211</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.33998</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.34849</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35108</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.34882</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.35238</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.35238</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.361</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.35819</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.37219</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.34887</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.34879</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.34349</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.34418</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35023</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.34169</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.32437</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>1.25803</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.45201</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.77418</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.52737</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.80747</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.44485</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.6146</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.33599</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.3241</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.87314</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.36178</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.38137</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.29994</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.28787</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.32541</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.29493</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.28802</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.30562</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.3369</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.34646</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.6368200000000001</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.36991</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.34287</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.33956</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.41477</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.34077</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.6786799999999999</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.53134</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.8119700000000001</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.70473</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>1.17692</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.6640199999999999</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.64118</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.34573</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.8714400000000001</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.67015</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.86014</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.35669</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>1.2278</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>1.21762</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>1.25313</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.9721900000000001</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.92998</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>1.28012</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.82035</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>1.05207</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.83147</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>1.67336</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.81668</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.72793</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>1.27967</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>1.20455</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.70069</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.40229</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.39364</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.36404</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.36738</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.35467</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.34869</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34576</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.44867</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.51842</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.46726</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.6035199999999999</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.3921</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.39216</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.38157</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.38603</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.38579</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.39153</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.37883</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.38696</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.39078</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.38902</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.37711</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.38026</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.39122</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.36791</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.38963</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.3697</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.37131</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.37539</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.38664</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.37302</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.40755</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.41037</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.49298</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.4518</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.41524</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.44921</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.41387</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.57665</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>1.20173</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.8663999999999999</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>1.249</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>1.28565</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>1.64219</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>1.36523</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.42683</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.3626</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.34727</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.35503</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.53752</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.5401900000000001</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.5638500000000001</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.6743300000000001</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.5364800000000001</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.45545</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.48681</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.47791</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.5572999999999999</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.80633</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.84235</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>1.14604</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.5306799999999999</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.53761</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.52103</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.52025</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.8035399999999999</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.33927</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.31607</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.3342</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.3488</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.33685</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.35494</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.35088</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.35252</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.35783</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.36867</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.34393</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.36113</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.33101</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.38915</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.40817</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.4512</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.41461</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.46391</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.46398</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.49527</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.60609</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.70784</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.79632</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.57262</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.6925800000000001</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.74517</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.7589</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.71196</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.76409</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.61676</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.66492</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.77862</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.6099</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.4412</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.43796</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.43119</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.39338</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.49616</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.4012</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.41147</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.42128</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.42686</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.41677</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.413</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.40851</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.37769</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.40825</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.37007</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.37645</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.44504</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.36642</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.36179</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.35584</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.35255</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.34935</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.35833</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.281</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.34711</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.34091</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.35222</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.35833</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.35847</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.36318</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.37189</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.34744</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.35375</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.34752</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.37185</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.39443</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.35686</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.38045</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.39166</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.37677</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.37898</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35139</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.35836</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.33868</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.33379</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.34102</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.36825</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>1.55063</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.53523</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.50617</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.50326</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.52415</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.51324</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.70025</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.5252100000000001</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.60154</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.5618099999999999</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.6108300000000001</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>1.11379</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.34864</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.16337</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.22444</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.30349</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.29983</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32199</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.34267</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.3344</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.33693</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.33752</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.35517</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.37648</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.37593</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.53277</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.43603</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.33091</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.42296</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.40984</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.41987</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.40048</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.38919</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.34306</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.34608</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.36479</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.37412</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.32271</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.33355</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.36791</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.36517</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.35252</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.35742</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35411</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.37096</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.32974</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.35439</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.30925</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.34277</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.32964</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.32512</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.29315</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.4516</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.79514</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.36872</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.35206</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.71646</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.33877</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.3041</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.28236</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.33234</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.26677</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.26435</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.30405</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.26436</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.30933</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.34382</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.30312</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.25263</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.2872</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.29482</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.30385</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.29074</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.29517</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.2996</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.24537</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.30402</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.24448</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.23817</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.32175</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.28357</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.27529</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.30659</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.23311</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.3421</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.30602</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.30617</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.30058</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.18091</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.28175</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.24896</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.2702</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.26498</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.26092</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.08973</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.31606</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.30789</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.26521</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.25879</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.03253</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.28903</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.28213</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.20049</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.27632</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.31135</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.31269</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.30724</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.25274</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.27126</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.25749</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.24179</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.27627</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.28492</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.27335</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.32081</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.32217</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.31531</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.33761</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.3351</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.34496</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.36036</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.33993</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.35502</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.3506</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.38125</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.37454</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.43834</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.30139</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.34726</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.33648</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.3501</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.32936</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.33556</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.35409</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.32926</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.42376</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.36499</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.40007</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.33414</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.3349</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.31909</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.32999</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.32424</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.30093</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.32932</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.30066</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.31834</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.298</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.56588</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.32543</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.32522</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.32809</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.32618</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.26005</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.28832</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.28394</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.30466</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.22768</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.2824700000000001</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.28652</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.2393</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.22646</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.22982</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.22981</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.22671</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.22671</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.22857</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.27799</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.22277</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.22671</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.22701</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.27653</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.2266</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.2264</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.32554</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.23374</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.15549</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.26561</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.2022</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.01166</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00043</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>-0.00023</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04957</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.14526</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.02126</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03957</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.01544</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04286</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.04075</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04859</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04824000000000001</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02446</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.02923</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.0494</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>5.999999999999999e-05</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.27431</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04964</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.0493</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.03833</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.01934</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04958</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04963</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.03618</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.20119</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.26467</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.28812</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.279</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.30299</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.30712</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.23103</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.30946</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.32687</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.3425</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.33547</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.33853</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.30864</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.31393</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.34779</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.33647</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.34053</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.33907</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.33732</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.34217</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.33618</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.36267</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.41419</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.35134</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.36459</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.34669</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.34214</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.34143</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.33345</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.34386</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.31223</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.32779</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.7118099999999999</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.61366</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.38137</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.40303</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.3867</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.40806</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.41506</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.35576</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.28228</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.3377</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.30123</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.29719</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.29269</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.24227</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.29457</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.27936</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.23917</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.22427</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.25775</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.24912</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.27714</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.24341</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.27021</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.2816</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.30353</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.43528</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.34912</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.33752</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.34488</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.24927</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.35999</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.6319900000000001</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.8058200000000001</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.87552</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.8508</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.32572</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.38064</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>-0.04981</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.03922</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.05559</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.29841</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.3005</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.22994</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.2482</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.31892</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.18914</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.21022</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.23738</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.29306</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.2638</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.29296</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.25702</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.25185</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.26249</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.26201</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.18508</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.24305</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.47134</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.04676</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.2764</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.09701</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.12557</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.13709</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.09543</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.11925</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.10959</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.13871</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.94936</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.52655</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.22403</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.24904</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.8089700000000001</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.47961</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.48898</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.5722699999999999</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.77164</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.49055</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.83916</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.83736</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.8416699999999999</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.9389400000000001</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.7296699999999999</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.7676000000000001</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.73324</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.37391</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.35348</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.37083</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.36047</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.3603</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.45842</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.59376</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.60917</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.5565099999999999</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.49227</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.45228</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.39572</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.37944</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.36648</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.34701</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.32848</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.33238</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.32192</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.31344</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.46318</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.31463</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.30767</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.30867</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.29865</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.30301</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.26429</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.33305</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.33178</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.35846</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.45302</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.46195</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.35967</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.37644</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.32054</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.31949</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.32888</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.4173</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.37363</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.44122</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.16087</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.13642</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.10039</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.08837</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.0882</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.06781999999999999</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.3112799999999999</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.08423</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.06548999999999999</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>-0.03267</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.06818</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.05929</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.0291</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.31382</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.05707</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.05461999999999999</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.07415999999999999</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.31655</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.30287</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.30974</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.33123</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.33443</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.15786</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.06673</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.05867</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.09456999999999999</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.08291</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.10809</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.14843</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.13468</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.12006</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.09598999999999999</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.12004</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.2107</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.4011</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.38271</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.45745</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.34925</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.35209</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.33541</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.33648</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.33341</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.41499</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.41719</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.40266</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.38539</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.37876</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.37479</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.37239</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.35382</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.35588</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.34858</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.34827</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.34406</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.34528</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.34311</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.33962</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.34874</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.33319</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.33248</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.32638</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.32843</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.32996</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.33004</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.33985</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.33242</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.34766</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.34078</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.34837</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.34205</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.35136</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.39634</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.36133</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.35231</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.5316799999999999</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.74687</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.26761</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.03226</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.18306</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.09543</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.10327</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.13647</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.101</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.13385</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.09798</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.05302</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.17854</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.15644</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.17261</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.17081</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.13242</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.09048</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.17456</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.07604999999999999</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.0737</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.15618</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.08885</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.07920000000000001</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.0837</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.07304000000000001</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.09372</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.09379000000000001</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.63724</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.32478</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>-0.02447</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>1.74589</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.57401</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.24881</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.5567799999999999</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.21138</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.55367</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.37654</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.19262</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.03735</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.44616</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.44404</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.5906399999999999</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.6630499999999999</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.7668400000000001</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.44919</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.4183</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.35071</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.41243</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.374</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.35343</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.3759</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.36017</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.23172</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.35257</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.34063</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.34894</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.33602</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.44875</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.37745</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.37277</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.36547</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.36122</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.34371</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.35263</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.3635</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.35719</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.35563</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.352</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.34814</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.34487</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.34254</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.34386</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.34348</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.33647</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.31754</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.3366</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.33111</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.32904</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.32705</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.33871</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.33526</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.34536</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.36521</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.34782</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.3545</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.34194</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.34909</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.34758</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.34581</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.37887</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.39125</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.36338</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.3539</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.43496</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.37995</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.36043</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.37281</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.35336</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.31055</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.36362</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.82087</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.39413</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.52539</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.39925</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.2926</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.54264</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.37902</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.46406</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.31621</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33661</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.34371</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.32532</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33353</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.34174</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.33822</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.32487</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.34422</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.34291</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.36605</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.3634</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.37001</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.43858</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.37364</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.39273</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.37199</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.37262</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.41637</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.40992</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.51115</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.7642599999999999</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.69259</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>1.56586</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.65608</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.97668</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.61485</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.47086</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>1.13125</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.90576</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>1.12975</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>1.02518</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.94543</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.7775700000000001</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.6109199999999999</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.6183099999999999</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.41329</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.35628</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.36001</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.34939</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.35335</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.29941</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.35747</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.34489</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.34763</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.33812</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.32318</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.33454</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.32807</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.32976</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.34123</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.32008</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.36142</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.34102</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.33055</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.33629</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.33348</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.20519</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.32195</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.32431</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.33631</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.32376</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.33147</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.34437</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.33951</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.33308</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.37365</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.37364</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.35128</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.33714</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.33476</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.33625</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.35816</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.33385</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.34657</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.34969</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.33489</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.3441</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.41664</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>1.14427</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.8386699999999999</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.47048</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.68235</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.86994</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.5061100000000001</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>1.15502</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.89147</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.33838</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>1.73999</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.47486</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.44442</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.91575</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.56659</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>1.34064</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.83163</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>1.18342</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.47051</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.82352</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.94576</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.82482</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.4914</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.34825</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.34026</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.41329</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.40063</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.35987</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.42514</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.85129</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.74281</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.40957</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.3642</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.53554</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.9374600000000001</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.47824</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.55203</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>1.23275</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.57957</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.8652300000000001</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.45321</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.61297</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>1.26487</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.56112</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.60241</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.56524</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.80737</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.39606</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.42057</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.40121</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.36702</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.38263</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.45832</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.34615</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.35975</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.34268</v>
+      </c>
+      <c r="C142" t="n">
+        <v>1.10516</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.73773</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.55303</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.5815900000000001</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.80511</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.36388</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.43566</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.37012</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.37945</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.36817</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.3665</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.36991</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.36599</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.36219</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.36575</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.36585</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.36492</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.36555</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.36103</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.35549</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.35675</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.35996</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.35781</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.35669</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.34718</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.35629</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.35107</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.36901</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.35619</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.34374</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.34571</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.35046</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.35783</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.35987</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.35461</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.34164</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.37379</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.36408</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.35563</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.36257</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.6547200000000001</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.40661</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.34673</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.34883</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.44113</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.32349</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.34307</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.35169</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.58594</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.33988</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.33647</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.42823</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.3469100000000001</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.82317</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.64877</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.33673</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.32287</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.33653</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.34992</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.32336</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.35606</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.35813</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.32956</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.35389</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.34509</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.34834</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.37249</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.43439</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.42552</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.4019</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.38194</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.35381</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.36132</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.38111</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.42894</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.44588</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.55131</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.50601</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.47735</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.43168</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.38175</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.4247</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.39276</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.87491</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>1.06031</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.81692</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.49302</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.60325</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.6896100000000001</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.63874</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.4415</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.35492</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.35516</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.35605</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.35664</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.34821</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.41034</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.38337</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.36104</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.37147</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.37451</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.37285</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.36487</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.3667</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.36032</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.3654</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.35641</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.35826</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.36091</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.34995</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.36441</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.35115</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.35572</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.35403</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.35506</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.35114</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.35141</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.35382</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.35252</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.35506</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.34631</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.34146</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.35278</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.34728</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.34758</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.31191</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.31734</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.31716</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.17556</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.30609</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.29457</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.31062</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.14524</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.19789</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.142</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.29112</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04466</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.12165</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.33045</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.2264</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.26633</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.15113</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.144</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.28921</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.19602</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.30482</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.22602</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.26137</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.15251</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.35606</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.30759</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.15249</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.3128</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.29934</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.19628</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.14194</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.27883</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.37952</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.32206</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.32101</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.39552</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.2956</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.33317</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.34634</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.33676</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.39697</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.40463</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.41689</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.38387</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.8167300000000001</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.60736</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.46821</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>1.05473</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.34262</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.40644</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.36091</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.48871</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.43529</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.38037</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.38829</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.4324</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.38314</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.48758</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.39504</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.48238</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.43675</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.43998</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.45701</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.38264</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.38148</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.38271</v>
       </c>
     </row>
   </sheetData>
